--- a/output/graficos_dimensiones/comunal_e_supneta_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supneta_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:09</t>
+    <t xml:space="preserve">2026-09-10 00:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_supneta_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supneta_a_2022_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:13</t>
+    <t xml:space="preserve">2026-09-18 10:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
